--- a/docker/final_master_seed/TRANSACTIONS_MASTER_V5_HARD_RECON_FIXES.xlsx
+++ b/docker/final_master_seed/TRANSACTIONS_MASTER_V5_HARD_RECON_FIXES.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4420" yWindow="780" windowWidth="31580" windowHeight="22600" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="READ_ME_DYNAMATIC" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Review Needed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Corporate Action Audit" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Reconciliation Fix Audit" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Targeted Validation" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="2012 Reconciliation Policy" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="2012 Snapshot Quality" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="2012 Reconciliation Audit" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="2012 Reconciliation Summary" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Version Info" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="V5 Hard Recon Audit" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="V5 Validation" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="READ_ME_DYNAMATIC" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Needed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corporate Action Audit" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation Fix Audit" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targeted Validation" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2012 Reconciliation Policy" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2012 Snapshot Quality" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2012 Reconciliation Audit" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2012 Reconciliation Summary" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Version Info" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5 Hard Recon Audit" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5 Validation" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
@@ -27,12 +27,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="166" formatCode="#,##0;[Red]\(#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="#,##0.00;[Red]\(#,##0.00\);\-"/>
     <numFmt numFmtId="168" formatCode="dd\-mmm\-yyyy\ hh:mm"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -253,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -507,6 +508,7 @@
     <xf numFmtId="0" fontId="11" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2409,7 +2411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N526"/>
+  <dimension ref="A1:N532"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -17250,6 +17252,180 @@
       <c r="I526" s="77" t="n"/>
       <c r="J526" s="77" t="n"/>
       <c r="K526" s="77" t="n"/>
+    </row>
+    <row r="527">
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>HEG</t>
+        </is>
+      </c>
+      <c r="C527" s="89" t="n">
+        <v>46227</v>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>562</v>
+      </c>
+      <c r="F527" t="n">
+        <v>643.95</v>
+      </c>
+      <c r="G527" t="n">
+        <v>358036</v>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>Portfolio_2026.xlsx / 24Jul26: Add 562@643.95 = 358036</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Aurionpro</t>
+        </is>
+      </c>
+      <c r="C528" s="89" t="n">
+        <v>46231</v>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>-604</v>
+      </c>
+      <c r="F528" t="n">
+        <v>745.9299999999999</v>
+      </c>
+      <c r="G528" t="n">
+        <v>450542</v>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>Portfolio_2026.xlsx / 28Jul26: Sell 604@745.93 = 450542</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>AtherEnerg</t>
+        </is>
+      </c>
+      <c r="C529" s="89" t="n">
+        <v>46238</v>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>315</v>
+      </c>
+      <c r="F529" t="n">
+        <v>1451.14</v>
+      </c>
+      <c r="G529" t="n">
+        <v>457109</v>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>Portfolio_2026.xlsx / 04Aug26: Add 315@1451.14 = 457109</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>WelEnt</t>
+        </is>
+      </c>
+      <c r="C530" s="89" t="n">
+        <v>46238</v>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>-465</v>
+      </c>
+      <c r="F530" t="n">
+        <v>580.92</v>
+      </c>
+      <c r="G530" t="n">
+        <v>270128</v>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>Portfolio_2026.xlsx / 04Aug26: Sell 465@580.92 = 270128</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>HEG</t>
+        </is>
+      </c>
+      <c r="C531" s="89" t="n">
+        <v>46244</v>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>550</v>
+      </c>
+      <c r="F531" t="n">
+        <v>683.63</v>
+      </c>
+      <c r="G531" t="n">
+        <v>375997</v>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>Portfolio_2026.xlsx / 10Aug26: Add 550@683.63 = 375997</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>WelEnt</t>
+        </is>
+      </c>
+      <c r="C532" s="89" t="n">
+        <v>46244</v>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>-1389</v>
+      </c>
+      <c r="F532" t="n">
+        <v>581.25</v>
+      </c>
+      <c r="G532" t="n">
+        <v>807356</v>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>Portfolio_2026.xlsx / 10Aug26: Sell 1389@581.25 = 807356</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D427">
